--- a/jeu_du_moulin_boura/rpt/ressource/BOM_Modifiee.xlsx
+++ b/jeu_du_moulin_boura/rpt/ressource/BOM_Modifiee.xlsx
@@ -790,16 +790,72 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -823,48 +879,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -882,20 +896,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -913,6 +913,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1224,13 +1228,13 @@
     <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:14" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="45" t="str">
+      <c r="B3" s="42" t="str">
         <f>CONCATENATE("",Sheet2!A5)</f>
         <v xml:space="preserve">  1.0.0</v>
       </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
       <c r="F3" s="25"/>
       <c r="G3" s="15" t="s">
         <v>4</v>
@@ -1239,13 +1243,13 @@
         <v>0</v>
       </c>
       <c r="I3" s="3"/>
-      <c r="J3" s="39" t="s">
+      <c r="J3" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="41"/>
+      <c r="K3" s="60"/>
+      <c r="L3" s="60"/>
+      <c r="M3" s="60"/>
+      <c r="N3" s="61"/>
     </row>
     <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
@@ -1261,33 +1265,33 @@
     </row>
     <row r="5" spans="1:14" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="52" t="s">
+      <c r="B5" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="53"/>
+      <c r="C5" s="52"/>
       <c r="D5" s="5"/>
       <c r="E5" s="10" t="s">
         <v>2</v>
       </c>
       <c r="F5" s="6"/>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="37" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="55"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
-      <c r="B6" s="32" t="str">
+      <c r="B6" s="40" t="str">
         <f>Sheet2!A4</f>
         <v>1.0.0</v>
       </c>
-      <c r="C6" s="33"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="26" t="s">
         <v>9</v>
       </c>
@@ -1295,14 +1299,14 @@
         <v>114</v>
       </c>
       <c r="F6" s="6"/>
-      <c r="G6" s="43"/>
+      <c r="G6" s="38"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
     </row>
     <row r="7" spans="1:14" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
@@ -1310,15 +1314,15 @@
       <c r="C7" s="14"/>
       <c r="D7" s="6"/>
       <c r="E7" s="12"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="44"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="39"/>
       <c r="H7" s="11"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
@@ -1331,10 +1335,10 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="55"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
@@ -1342,15 +1346,15 @@
       <c r="C9" s="14"/>
       <c r="D9" s="6"/>
       <c r="E9" s="12"/>
-      <c r="F9" s="63"/>
+      <c r="F9" s="32"/>
       <c r="G9" s="23"/>
       <c r="H9" s="11"/>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="55"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
@@ -1360,13 +1364,13 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="38"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="58"/>
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
@@ -1383,14 +1387,14 @@
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="49" t="str">
+      <c r="B12" s="48" t="str">
         <f>B3</f>
         <v xml:space="preserve">  1.0.0</v>
       </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="64"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="33"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1401,15 +1405,15 @@
       <c r="A13" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="48"/>
-      <c r="D13" s="54" t="s">
+      <c r="C13" s="45"/>
+      <c r="D13" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="65" t="s">
+      <c r="E13" s="54"/>
+      <c r="F13" s="34" t="s">
         <v>111</v>
       </c>
       <c r="G13" s="8" t="s">
@@ -1442,15 +1446,15 @@
         <f t="shared" ref="A14:A34" si="0">ROW(B13) - ROW($B$12)</f>
         <v>1</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="47">
         <v>1</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32" t="s">
+      <c r="C14" s="47"/>
+      <c r="D14" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="66"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="17" t="s">
         <v>34</v>
       </c>
@@ -1474,15 +1478,15 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="46">
         <v>5</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="32" t="s">
+      <c r="C15" s="46"/>
+      <c r="D15" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="33"/>
-      <c r="F15" s="66"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="35"/>
       <c r="G15" s="17" t="s">
         <v>35</v>
       </c>
@@ -1506,15 +1510,15 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="47">
         <v>3</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32" t="s">
+      <c r="C16" s="47"/>
+      <c r="D16" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="66"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="17" t="s">
         <v>36</v>
       </c>
@@ -1538,15 +1542,15 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B17" s="34">
+      <c r="B17" s="46">
         <v>4</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="32" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="33"/>
-      <c r="F17" s="66"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="17" t="s">
         <v>37</v>
       </c>
@@ -1570,15 +1574,15 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="47">
         <v>24</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32" t="s">
+      <c r="C18" s="47"/>
+      <c r="D18" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="33"/>
-      <c r="F18" s="67"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="36"/>
       <c r="G18" s="17" t="s">
         <v>16</v>
       </c>
@@ -1610,15 +1614,15 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="46">
         <v>1</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="32" t="s">
+      <c r="C19" s="46"/>
+      <c r="D19" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="33"/>
-      <c r="F19" s="67"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="36"/>
       <c r="G19" s="17" t="s">
         <v>38</v>
       </c>
@@ -1650,15 +1654,15 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="47">
         <v>1</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="32" t="s">
+      <c r="C20" s="47"/>
+      <c r="D20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="67"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="36"/>
       <c r="G20" s="17" t="s">
         <v>39</v>
       </c>
@@ -1690,15 +1694,15 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="46">
         <v>1</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="32" t="s">
+      <c r="C21" s="46"/>
+      <c r="D21" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="67"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="36"/>
       <c r="G21" s="17" t="s">
         <v>40</v>
       </c>
@@ -1730,15 +1734,15 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="47">
         <v>1</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32" t="s">
+      <c r="C22" s="47"/>
+      <c r="D22" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="67"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="36"/>
       <c r="G22" s="17" t="s">
         <v>41</v>
       </c>
@@ -1770,14 +1774,14 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="46">
         <v>1</v>
       </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="32" t="s">
+      <c r="C23" s="46"/>
+      <c r="D23" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="33"/>
+      <c r="E23" s="41"/>
       <c r="F23" s="24" t="s">
         <v>113</v>
       </c>
@@ -1802,15 +1806,15 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="47">
         <v>11</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="47"/>
+      <c r="D24" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="66"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="17" t="s">
         <v>43</v>
       </c>
@@ -1832,15 +1836,15 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B25" s="34">
+      <c r="B25" s="46">
         <v>1</v>
       </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="32" t="s">
+      <c r="C25" s="46"/>
+      <c r="D25" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="66"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="17" t="s">
         <v>44</v>
       </c>
@@ -1862,15 +1866,15 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="47">
         <v>1</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32" t="s">
+      <c r="C26" s="47"/>
+      <c r="D26" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="66"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="17" t="s">
         <v>45</v>
       </c>
@@ -1892,15 +1896,15 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B27" s="34">
+      <c r="B27" s="46">
         <v>2</v>
       </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="32" t="s">
+      <c r="C27" s="46"/>
+      <c r="D27" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="67"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="36"/>
       <c r="G27" s="17" t="s">
         <v>46</v>
       </c>
@@ -1932,15 +1936,15 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="47">
         <v>11</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32" t="s">
+      <c r="C28" s="47"/>
+      <c r="D28" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="66"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="17" t="s">
         <v>47</v>
       </c>
@@ -1962,15 +1966,15 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="46">
         <v>1</v>
       </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="46"/>
+      <c r="D29" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="33"/>
-      <c r="F29" s="67"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="36"/>
       <c r="G29" s="17" t="s">
         <v>48</v>
       </c>
@@ -2002,15 +2006,15 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B30" s="31">
+      <c r="B30" s="47">
         <v>2</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="32" t="s">
+      <c r="C30" s="47"/>
+      <c r="D30" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="66"/>
+      <c r="E30" s="41"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="17" t="s">
         <v>49</v>
       </c>
@@ -2042,15 +2046,15 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="46">
         <v>2</v>
       </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="32" t="s">
+      <c r="C31" s="46"/>
+      <c r="D31" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="66"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="17" t="s">
         <v>50</v>
       </c>
@@ -2082,14 +2086,14 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B32" s="31">
+      <c r="B32" s="47">
         <v>4</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="32" t="s">
+      <c r="C32" s="47"/>
+      <c r="D32" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="33"/>
+      <c r="E32" s="41"/>
       <c r="F32" s="24" t="s">
         <v>112</v>
       </c>
@@ -2114,14 +2118,14 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="46">
         <v>1</v>
       </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="46"/>
+      <c r="D33" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="33"/>
+      <c r="E33" s="41"/>
       <c r="F33" s="24" t="s">
         <v>112</v>
       </c>
@@ -2146,15 +2150,15 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="47">
         <v>1</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="32" t="s">
+      <c r="C34" s="47"/>
+      <c r="D34" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="33"/>
-      <c r="F34" s="67"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="36"/>
       <c r="G34" s="17" t="s">
         <v>53</v>
       </c>
@@ -2198,6 +2202,51 @@
     <row r="37" spans="1:14" ht="15" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K7:N7"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="B3:E3"/>
@@ -2209,51 +2258,6 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="J3:N3"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2273,11 +2277,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
@@ -2332,13 +2336,13 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="e">
+      <c r="A13" s="65" t="e">
         <f>CONCATENATE(Sheet2!A18,"[",Sheet2!#REF!,"]",Sheet2!#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="61"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="67"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -2362,15 +2366,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010098AFC7C83C7C054E95F4B42F91168742" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="66e3d8284d9fc5410f6939df54f0caa6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c73ba516-6d34-4b92-a096-ac7dfb020022" xmlns:ns3="ebd706b7-678b-40df-972d-f0eaa6262b36" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea909251fc86ece970dc0ed8cbb70340" ns2:_="" ns3:_="">
     <xsd:import namespace="c73ba516-6d34-4b92-a096-ac7dfb020022"/>
@@ -2577,15 +2572,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C64E99E-77F3-4A44-9FA2-482228DEF9ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCF1807D-2C11-4442-B446-3E1610E4AAB8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2602,4 +2598,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C64E99E-77F3-4A44-9FA2-482228DEF9ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>